--- a/backend/design-capital-structure/design-capital-structure-template.xlsx
+++ b/backend/design-capital-structure/design-capital-structure-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/NICCP-AI/backend/design-capital-structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="237" documentId="8_{E5295D48-A9F0-4D2F-8DCF-7C23BD8E24E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C9CECFB-3C08-4AA9-95F0-9F68B396126B}"/>
+  <xr:revisionPtr revIDLastSave="246" documentId="8_{E5295D48-A9F0-4D2F-8DCF-7C23BD8E24E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{810DF5EA-54BA-4B74-993B-B5BA7347208C}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{BBCF56CD-8AD5-4002-91F7-ED7A4CE8CFDA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{BBCF56CD-8AD5-4002-91F7-ED7A4CE8CFDA}"/>
   </bookViews>
   <sheets>
     <sheet name="JUST ACCESS" sheetId="2" r:id="rId1"/>
@@ -88,9 +88,6 @@
     <t>2.- Grants (inyected in the first two years but linked to CAPEX deployment)</t>
   </si>
   <si>
-    <t>Unit</t>
-  </si>
-  <si>
     <t>Financiation</t>
   </si>
   <si>
@@ -113,6 +110,9 @@
   </si>
   <si>
     <t>Type</t>
+  </si>
+  <si>
+    <t>Units</t>
   </si>
 </sst>
 </file>
@@ -852,13 +852,13 @@
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
         <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:36" ht="16" x14ac:dyDescent="0.35">
@@ -944,19 +944,19 @@
     </row>
     <row r="5" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="D5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
@@ -1183,10 +1183,10 @@
       <c r="A13" s="2"/>
       <c r="B13" s="1"/>
       <c r="C13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>7</v>
@@ -1425,7 +1425,7 @@
       <c r="A15" s="2"/>
       <c r="B15" s="1"/>
       <c r="C15" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>10</v>
@@ -1657,13 +1657,13 @@
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
         <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
       </c>
       <c r="AM1" s="14"/>
       <c r="AN1" s="14"/>
@@ -1757,19 +1757,19 @@
     </row>
     <row r="5" spans="1:40" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="D5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
@@ -2008,10 +2008,10 @@
       <c r="A13" s="2"/>
       <c r="B13" s="1"/>
       <c r="C13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>7</v>
@@ -2250,7 +2250,7 @@
       <c r="A15" s="2"/>
       <c r="B15" s="1"/>
       <c r="C15" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>10</v>
@@ -2515,13 +2515,13 @@
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
         <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:36" ht="16" x14ac:dyDescent="0.35">
@@ -2607,19 +2607,19 @@
     </row>
     <row r="5" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="D5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
@@ -2846,10 +2846,10 @@
       <c r="A13" s="2"/>
       <c r="B13" s="1"/>
       <c r="C13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>7</v>
@@ -3088,7 +3088,7 @@
       <c r="A15" s="2"/>
       <c r="B15" s="1"/>
       <c r="C15" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>10</v>

--- a/backend/design-capital-structure/design-capital-structure-template.xlsx
+++ b/backend/design-capital-structure/design-capital-structure-template.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/NICCP-AI/backend/design-capital-structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="246" documentId="8_{E5295D48-A9F0-4D2F-8DCF-7C23BD8E24E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{810DF5EA-54BA-4B74-993B-B5BA7347208C}"/>
+  <xr:revisionPtr revIDLastSave="249" documentId="8_{E5295D48-A9F0-4D2F-8DCF-7C23BD8E24E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{080BD826-EE86-4273-BF9A-A1403C8DD670}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{BBCF56CD-8AD5-4002-91F7-ED7A4CE8CFDA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{BBCF56CD-8AD5-4002-91F7-ED7A4CE8CFDA}"/>
   </bookViews>
   <sheets>
-    <sheet name="JUST ACCESS" sheetId="2" r:id="rId1"/>
-    <sheet name="Electricity" sheetId="1" r:id="rId2"/>
+    <sheet name="E-Cooking" sheetId="1" r:id="rId1"/>
+    <sheet name="Electricity" sheetId="2" r:id="rId2"/>
     <sheet name="LPG" sheetId="3" r:id="rId3"/>
   </sheets>
   <externalReferences>
@@ -841,812 +841,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C54003D-BBE9-46A5-976B-0C15632AF571}">
-  <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:AJ16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="30.6328125" customWidth="1"/>
-    <col min="3" max="3" width="71.6328125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:36" ht="16" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="1">
-        <v>0</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-    </row>
-    <row r="3" spans="1:36" ht="16" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1">
-        <v>0</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
-      <c r="R3" s="1"/>
-      <c r="S3" s="1"/>
-      <c r="T3" s="1"/>
-      <c r="U3" s="1"/>
-    </row>
-    <row r="4" spans="1:36" ht="16" x14ac:dyDescent="0.35">
-      <c r="A4" s="2"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
-    </row>
-    <row r="5" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
-      <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
-      <c r="T5" s="1"/>
-      <c r="U5" s="1"/>
-    </row>
-    <row r="6" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="15">
-        <v>0</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="6">
-        <v>0</v>
-      </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
-      <c r="U6" s="1"/>
-    </row>
-    <row r="7" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="15">
-        <v>0</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
-      <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
-      <c r="T7" s="1"/>
-      <c r="U7" s="1"/>
-    </row>
-    <row r="8" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="15">
-        <v>0</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-      <c r="T8" s="1"/>
-      <c r="U8" s="1"/>
-    </row>
-    <row r="9" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" s="6">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
-    </row>
-    <row r="10" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="1"/>
-      <c r="S10" s="1"/>
-      <c r="T10" s="1"/>
-      <c r="U10" s="1"/>
-    </row>
-    <row r="11" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0</v>
-      </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
-    </row>
-    <row r="12" spans="1:36" ht="16" x14ac:dyDescent="0.35">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
-      <c r="S12" s="1"/>
-      <c r="T12" s="1"/>
-      <c r="U12" s="1"/>
-    </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A13" s="2"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" s="9">
-        <v>2020</v>
-      </c>
-      <c r="G13" s="9">
-        <v>2021</v>
-      </c>
-      <c r="H13" s="9">
-        <v>2022</v>
-      </c>
-      <c r="I13" s="9">
-        <v>2023</v>
-      </c>
-      <c r="J13" s="9">
-        <v>2024</v>
-      </c>
-      <c r="K13" s="9">
-        <v>2025</v>
-      </c>
-      <c r="L13" s="9">
-        <v>2026</v>
-      </c>
-      <c r="M13" s="9">
-        <v>2027</v>
-      </c>
-      <c r="N13" s="9">
-        <v>2028</v>
-      </c>
-      <c r="O13" s="9">
-        <v>2029</v>
-      </c>
-      <c r="P13" s="9">
-        <v>2030</v>
-      </c>
-      <c r="Q13" s="9">
-        <v>2031</v>
-      </c>
-      <c r="R13" s="9">
-        <v>2032</v>
-      </c>
-      <c r="S13" s="9">
-        <v>2033</v>
-      </c>
-      <c r="T13" s="9">
-        <v>2034</v>
-      </c>
-      <c r="U13" s="9">
-        <v>2035</v>
-      </c>
-      <c r="V13" s="9">
-        <v>2036</v>
-      </c>
-      <c r="W13" s="9">
-        <v>2037</v>
-      </c>
-      <c r="X13" s="9">
-        <v>2038</v>
-      </c>
-      <c r="Y13" s="9">
-        <v>2039</v>
-      </c>
-      <c r="Z13" s="9">
-        <v>2040</v>
-      </c>
-      <c r="AA13" s="9">
-        <v>2041</v>
-      </c>
-      <c r="AB13" s="9">
-        <v>2042</v>
-      </c>
-      <c r="AC13" s="9">
-        <v>2043</v>
-      </c>
-      <c r="AD13" s="9">
-        <v>2044</v>
-      </c>
-      <c r="AE13" s="9">
-        <v>2045</v>
-      </c>
-      <c r="AF13" s="9">
-        <v>2046</v>
-      </c>
-      <c r="AG13" s="9">
-        <v>2047</v>
-      </c>
-      <c r="AH13" s="9">
-        <v>2048</v>
-      </c>
-      <c r="AI13" s="9">
-        <v>2049</v>
-      </c>
-      <c r="AJ13" s="9">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="14" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="2"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="1"/>
-      <c r="E14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!F22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="F14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!E22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="G14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!E22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="H14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!E22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="I14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!F22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="J14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!G22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="K14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!H22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="L14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!I22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="M14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!J22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="N14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!K22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="O14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!L22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="P14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!M22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="Q14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!N22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="R14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!O22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="S14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!P22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="T14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!Q22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="U14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!R22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="V14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!S22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="W14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!T22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="X14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!U22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="Y14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!V22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="Z14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!W22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="AA14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!X22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="AB14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!Y22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="AC14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!Z22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="AD14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!AA22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="AE14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!AB22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="AF14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!AC22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="AG14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!AD22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="AH14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!AE22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="AI14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!AF22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-      <c r="AJ14" s="11" t="str">
-        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!AG22&gt;0,"ok","increase debt")</f>
-        <v>increase debt</v>
-      </c>
-    </row>
-    <row r="15" spans="1:36" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="2"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="16">
-        <v>0</v>
-      </c>
-      <c r="F15" s="16">
-        <v>0</v>
-      </c>
-      <c r="G15" s="16">
-        <v>0</v>
-      </c>
-      <c r="H15" s="16">
-        <v>0</v>
-      </c>
-      <c r="I15" s="16">
-        <v>0</v>
-      </c>
-      <c r="J15" s="16">
-        <v>0</v>
-      </c>
-      <c r="K15" s="16">
-        <v>0</v>
-      </c>
-      <c r="L15" s="16">
-        <v>0</v>
-      </c>
-      <c r="M15" s="16">
-        <v>0</v>
-      </c>
-      <c r="N15" s="16">
-        <v>0</v>
-      </c>
-      <c r="O15" s="16">
-        <v>0</v>
-      </c>
-      <c r="P15" s="16">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="16">
-        <v>0</v>
-      </c>
-      <c r="R15" s="16">
-        <v>0</v>
-      </c>
-      <c r="S15" s="16">
-        <v>0</v>
-      </c>
-      <c r="T15" s="16">
-        <v>0</v>
-      </c>
-      <c r="U15" s="16">
-        <v>0</v>
-      </c>
-      <c r="V15" s="16">
-        <v>0</v>
-      </c>
-      <c r="W15" s="16">
-        <v>0</v>
-      </c>
-      <c r="X15" s="16">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="16">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="16">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="16">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="16">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="16">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="16">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="16">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="16">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="16">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="16">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ15" s="16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="2"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="13">
-        <v>0</v>
-      </c>
-      <c r="F16" s="13">
-        <v>0</v>
-      </c>
-      <c r="G16" s="13">
-        <v>0</v>
-      </c>
-      <c r="H16" s="13">
-        <v>0</v>
-      </c>
-      <c r="I16" s="13">
-        <v>0</v>
-      </c>
-      <c r="J16" s="13">
-        <v>0</v>
-      </c>
-      <c r="K16" s="13">
-        <v>0</v>
-      </c>
-      <c r="L16" s="13">
-        <v>0</v>
-      </c>
-      <c r="M16" s="13">
-        <v>0</v>
-      </c>
-      <c r="N16" s="13">
-        <v>0</v>
-      </c>
-      <c r="O16" s="13">
-        <v>0</v>
-      </c>
-      <c r="P16" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="13">
-        <v>0</v>
-      </c>
-      <c r="R16" s="13">
-        <v>0</v>
-      </c>
-      <c r="S16" s="13">
-        <v>0</v>
-      </c>
-      <c r="T16" s="13">
-        <v>0</v>
-      </c>
-      <c r="U16" s="13">
-        <v>0</v>
-      </c>
-      <c r="V16" s="13">
-        <v>0</v>
-      </c>
-      <c r="W16" s="13">
-        <v>0</v>
-      </c>
-      <c r="X16" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="13">
-        <v>0</v>
-      </c>
-      <c r="AD16" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF16" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG16" s="13">
-        <v>0</v>
-      </c>
-      <c r="AH16" s="13">
-        <v>0</v>
-      </c>
-      <c r="AI16" s="13">
-        <v>0</v>
-      </c>
-      <c r="AJ16" s="13">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="C14:AJ14">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
-      <formula>"increase debt"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
-      <formula>"ok"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD3833E1-9C55-460E-A922-AEA15E5E66A2}">
   <sheetPr codeName="Hoja2"/>
   <dimension ref="A1:AN23"/>
@@ -2489,6 +1683,812 @@
     <row r="23" spans="39:40" x14ac:dyDescent="0.35">
       <c r="AM23" s="14"/>
       <c r="AN23" s="14"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C14:AJ14">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+      <formula>"increase debt"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+      <formula>"ok"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C54003D-BBE9-46A5-976B-0C15632AF571}">
+  <sheetPr codeName="Hoja1"/>
+  <dimension ref="A1:AJ16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="30.6328125" customWidth="1"/>
+    <col min="3" max="3" width="71.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" ht="16" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+    </row>
+    <row r="3" spans="1:36" ht="16" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+    </row>
+    <row r="4" spans="1:36" ht="16" x14ac:dyDescent="0.35">
+      <c r="A4" s="2"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+    </row>
+    <row r="5" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+    </row>
+    <row r="6" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="15">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+    </row>
+    <row r="7" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="15">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+    </row>
+    <row r="8" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="15">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+    </row>
+    <row r="9" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+    </row>
+    <row r="10" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+    </row>
+    <row r="11" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+    </row>
+    <row r="12" spans="1:36" ht="16" x14ac:dyDescent="0.35">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A13" s="2"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="9">
+        <v>2020</v>
+      </c>
+      <c r="G13" s="9">
+        <v>2021</v>
+      </c>
+      <c r="H13" s="9">
+        <v>2022</v>
+      </c>
+      <c r="I13" s="9">
+        <v>2023</v>
+      </c>
+      <c r="J13" s="9">
+        <v>2024</v>
+      </c>
+      <c r="K13" s="9">
+        <v>2025</v>
+      </c>
+      <c r="L13" s="9">
+        <v>2026</v>
+      </c>
+      <c r="M13" s="9">
+        <v>2027</v>
+      </c>
+      <c r="N13" s="9">
+        <v>2028</v>
+      </c>
+      <c r="O13" s="9">
+        <v>2029</v>
+      </c>
+      <c r="P13" s="9">
+        <v>2030</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>2031</v>
+      </c>
+      <c r="R13" s="9">
+        <v>2032</v>
+      </c>
+      <c r="S13" s="9">
+        <v>2033</v>
+      </c>
+      <c r="T13" s="9">
+        <v>2034</v>
+      </c>
+      <c r="U13" s="9">
+        <v>2035</v>
+      </c>
+      <c r="V13" s="9">
+        <v>2036</v>
+      </c>
+      <c r="W13" s="9">
+        <v>2037</v>
+      </c>
+      <c r="X13" s="9">
+        <v>2038</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>2039</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>2040</v>
+      </c>
+      <c r="AA13" s="9">
+        <v>2041</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>2042</v>
+      </c>
+      <c r="AC13" s="9">
+        <v>2043</v>
+      </c>
+      <c r="AD13" s="9">
+        <v>2044</v>
+      </c>
+      <c r="AE13" s="9">
+        <v>2045</v>
+      </c>
+      <c r="AF13" s="9">
+        <v>2046</v>
+      </c>
+      <c r="AG13" s="9">
+        <v>2047</v>
+      </c>
+      <c r="AH13" s="9">
+        <v>2048</v>
+      </c>
+      <c r="AI13" s="9">
+        <v>2049</v>
+      </c>
+      <c r="AJ13" s="9">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="2"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!F22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="F14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!E22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="G14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!E22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="H14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!E22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="I14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!F22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="J14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!G22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="K14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!H22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="L14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!I22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="M14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!J22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="N14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!K22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="O14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!L22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="P14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!M22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="Q14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!N22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="R14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!O22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="S14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!P22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="T14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!Q22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="U14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!R22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="V14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!S22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="W14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!T22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="X14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!U22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="Y14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!V22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="Z14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!W22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="AA14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!X22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="AB14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!Y22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="AC14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!Z22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="AD14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!AA22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="AE14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!AB22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="AF14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!AC22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="AG14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!AD22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="AH14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!AE22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="AI14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!AF22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+      <c r="AJ14" s="11" t="str">
+        <f>IF('[1]CleanStep - JUSTACCESS - FFSS'!AG22&gt;0,"ok","increase debt")</f>
+        <v>increase debt</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="2"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="16">
+        <v>0</v>
+      </c>
+      <c r="F15" s="16">
+        <v>0</v>
+      </c>
+      <c r="G15" s="16">
+        <v>0</v>
+      </c>
+      <c r="H15" s="16">
+        <v>0</v>
+      </c>
+      <c r="I15" s="16">
+        <v>0</v>
+      </c>
+      <c r="J15" s="16">
+        <v>0</v>
+      </c>
+      <c r="K15" s="16">
+        <v>0</v>
+      </c>
+      <c r="L15" s="16">
+        <v>0</v>
+      </c>
+      <c r="M15" s="16">
+        <v>0</v>
+      </c>
+      <c r="N15" s="16">
+        <v>0</v>
+      </c>
+      <c r="O15" s="16">
+        <v>0</v>
+      </c>
+      <c r="P15" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="16">
+        <v>0</v>
+      </c>
+      <c r="R15" s="16">
+        <v>0</v>
+      </c>
+      <c r="S15" s="16">
+        <v>0</v>
+      </c>
+      <c r="T15" s="16">
+        <v>0</v>
+      </c>
+      <c r="U15" s="16">
+        <v>0</v>
+      </c>
+      <c r="V15" s="16">
+        <v>0</v>
+      </c>
+      <c r="W15" s="16">
+        <v>0</v>
+      </c>
+      <c r="X15" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="16">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="16">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="16">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="16">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="16">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="16">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="16">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="16">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="16">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="16">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="2"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="13">
+        <v>0</v>
+      </c>
+      <c r="F16" s="13">
+        <v>0</v>
+      </c>
+      <c r="G16" s="13">
+        <v>0</v>
+      </c>
+      <c r="H16" s="13">
+        <v>0</v>
+      </c>
+      <c r="I16" s="13">
+        <v>0</v>
+      </c>
+      <c r="J16" s="13">
+        <v>0</v>
+      </c>
+      <c r="K16" s="13">
+        <v>0</v>
+      </c>
+      <c r="L16" s="13">
+        <v>0</v>
+      </c>
+      <c r="M16" s="13">
+        <v>0</v>
+      </c>
+      <c r="N16" s="13">
+        <v>0</v>
+      </c>
+      <c r="O16" s="13">
+        <v>0</v>
+      </c>
+      <c r="P16" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="13">
+        <v>0</v>
+      </c>
+      <c r="R16" s="13">
+        <v>0</v>
+      </c>
+      <c r="S16" s="13">
+        <v>0</v>
+      </c>
+      <c r="T16" s="13">
+        <v>0</v>
+      </c>
+      <c r="U16" s="13">
+        <v>0</v>
+      </c>
+      <c r="V16" s="13">
+        <v>0</v>
+      </c>
+      <c r="W16" s="13">
+        <v>0</v>
+      </c>
+      <c r="X16" s="13">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="13">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="13">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="13">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="13">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C14:AJ14">
